--- a/data/processed/ibovespa_treated.xlsx
+++ b/data/processed/ibovespa_treated.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/processed/ibovespa_treated.xlsx
+++ b/data/processed/ibovespa_treated.xlsx
@@ -3980,7 +3980,7 @@
         <v>0.001010522331812425</v>
       </c>
       <c r="GG5" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GH5" t="n">
         <v>0.0004709827467994643</v>
@@ -4728,7 +4728,7 @@
         <v>0.0003857351660982999</v>
       </c>
       <c r="GG6" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GH6" t="n">
         <v>0.0001156976499547824</v>
@@ -63448,499 +63448,499 @@
         <v>-0.0004298643906572863</v>
       </c>
       <c r="BM85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="BN85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="BO85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="BP85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="BQ85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="BR85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="BS85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="BT85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="BU85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="BV85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="BW85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="BX85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="BY85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="BZ85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CA85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CB85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CC85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CD85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CE85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CF85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CG85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CH85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CI85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CJ85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CK85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CL85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CM85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CN85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CO85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CP85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CQ85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CR85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CS85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CT85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CU85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CV85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CW85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CX85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CY85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="CZ85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DA85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DB85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DC85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DF85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DG85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DH85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DI85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DJ85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DK85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DL85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DM85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DN85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DO85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DP85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DQ85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DR85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DS85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DT85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DU85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DV85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DW85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DX85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DY85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="DZ85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EA85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EB85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EC85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="ED85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EE85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EF85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EG85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EH85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EI85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EJ85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EK85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EL85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EM85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EN85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EO85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EP85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EQ85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="ER85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="ES85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="ET85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EU85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EV85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EW85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EX85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EY85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="EZ85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FA85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FB85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FC85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FD85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FE85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FF85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FG85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FH85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FI85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FJ85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FK85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FL85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FM85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FN85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FO85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FP85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FQ85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FR85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FS85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FT85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FU85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FV85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FW85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FX85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FY85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="FZ85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GA85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GB85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GC85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GD85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GE85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GF85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GG85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GH85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GI85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GJ85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GK85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GL85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GM85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GN85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GO85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GP85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GQ85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GR85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GS85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GT85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GU85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GV85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GW85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GX85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GY85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="GZ85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HA85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HB85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HC85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HD85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HE85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HF85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HG85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HH85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HI85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HJ85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HK85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HL85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HM85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HN85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HO85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HP85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HQ85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HR85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HS85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HT85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HU85" t="n">
-        <v>1.109793535662279e-05</v>
+        <v>9.14555050677062e-07</v>
       </c>
       <c r="HV85" t="n">
         <v>-0.0001725502981582139</v>
